--- a/backend/data/financials_by_company/1499.HK.xlsx
+++ b/backend/data/financials_by_company/1499.HK.xlsx
@@ -4043,7 +4043,7 @@
         <v>-11690000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>-0.022919998</v>
